--- a/0 Planning/Personal Learning Checklist.xlsx
+++ b/0 Planning/Personal Learning Checklist.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -556,7 +556,7 @@
       <c r="A3" s="4" t="inlineStr"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Describe the function of the ALU, Control Unit, registers (PC, MAR, MDR, CIR, ACC) and the three system buses</t>
+          <t>I can describe the roles of the ALU, Control Unit and the registers PC, MAR, MDR, CIR and ACC</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr"/>
@@ -567,7 +567,7 @@
       <c r="A4" s="4" t="inlineStr"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Explain the stages of the fetch-decode-execute cycle and how registers and buses interact during it</t>
+          <t>I can trace the fetch-decode-execute cycle, naming every register transfer and bus involved</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr"/>
@@ -578,7 +578,7 @@
       <c r="A5" s="4" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Apply the factors affecting CPU performance (clock speed, cores, cache, pipelining) to compare processors for a given scenario</t>
+          <t>I can explain how clock speed, cores, cache and pipelining affect CPU performance, with caveats</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
@@ -589,7 +589,7 @@
       <c r="A6" s="4" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Compare Von Neumann and Harvard architectures, including the modified/hybrid form used in contemporary CPUs</t>
+          <t>I can compare Von Neumann, Harvard and contemporary (modified Harvard) architectures with distinct differences</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
@@ -615,7 +615,7 @@
       <c r="A8" s="4" t="inlineStr"/>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Explain the differences between CISC and RISC processors and where each is used</t>
+          <t>I can give distinct differences between CISC and RISC processors and link each to a typical use</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr"/>
@@ -626,7 +626,7 @@
       <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Describe GPUs and their uses, including general-purpose (non-graphics) applications</t>
+          <t>I can explain how a GPU achieves high performance and identify workloads suited to GPUs, including GPGPU uses</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
@@ -637,7 +637,7 @@
       <c r="A10" s="4" t="inlineStr"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Apply knowledge of multicore and parallel processing to justify a processor choice for a given workload</t>
+          <t>I can describe multicore and parallel systems and explain what limits the benefit of adding cores</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
@@ -645,36 +645,36 @@
       <c r="E10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>I can justify a choice of processor type for a given scenario using hardware features</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>1.1.3</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Input, Output and Storage Devices</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Describe how magnetic, flash/solid-state and optical storage work and compare their pros and cons</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Explain the differences between RAM and ROM and how virtual memory and virtual/cloud storage work</t>
+          <t>I can justify a choice of input or output device for a given scenario, linking characteristics to requirements</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
@@ -685,7 +685,7 @@
       <c r="A14" s="4" t="inlineStr"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Apply device characteristics to justify suitable input, output and storage choices for a given scenario</t>
+          <t>I can describe how magnetic, flash and optical storage work and compare their suitability for different uses</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
@@ -693,25 +693,21 @@
       <c r="E14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1.2.1</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Operating Systems</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>I can explain the differences between RAM and ROM, including volatility and their contents</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr"/>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Describe how an operating system manages memory (paging, segmentation and virtual memory) and handles interrupts using the stack.</t>
+          <t>I can explain virtual storage, distinguishing virtual memory from virtual (cloud) storage</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
@@ -719,21 +715,25 @@
       <c r="E16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Compare CPU scheduling algorithms and explain the purpose of different types of operating system.</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>1.2.1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Operating Systems (part 1)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Explain the roles of the BIOS, device drivers and virtual machines in a computer system.</t>
+          <t>I can describe the purpose of an operating system and the resources it manages.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
@@ -741,25 +741,21 @@
       <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>1.2.2</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Applications Generation</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>I can explain memory management using paging, segmentation and virtual memory, including their drawbacks.</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr"/>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Distinguish application, utility and open/closed source software and select appropriate examples.</t>
+          <t>I can describe the full sequence the OS follows when servicing an interrupt, including the role of the stack.</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
@@ -770,7 +766,7 @@
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Compare assemblers, compilers and interpreters and describe the four stages of compilation in order.</t>
+          <t>I can compare round robin, FIFO, shortest job first, shortest remaining time and multilevel feedback queue scheduling.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr"/>
@@ -778,36 +774,36 @@
       <c r="E21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Explain the roles of libraries, linkers and loaders, including static versus dynamic linking.</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>1.2.2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Applications Generation</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>1.2.3</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>I can distinguish applications, systems software and utilities, and compare open and closed source software.</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Compare the Waterfall, Agile, Extreme Programming, Spiral and RAD methodologies and their trade-offs.</t>
+          <t>I can compare assemblers, compilers and interpreters and choose the right translator for a scenario.</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr"/>
@@ -818,7 +814,7 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Describe the stages of the software development lifecycle from analysis to evaluation.</t>
+          <t>I can describe the four stages of compilation, in order, with what each produces.</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr"/>
@@ -829,7 +825,7 @@
       <c r="A26" s="4" t="inlineStr"/>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Select and justify a suitable methodology for a given scenario using its clues.</t>
+          <t>I can explain the roles of libraries, linkers and loaders, including static versus dynamic linking.</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr"/>
@@ -839,12 +835,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1.2.4</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Types of Programming Language</t>
+          <t>Software Development</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
@@ -855,7 +851,7 @@
       <c r="A28" s="4" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Explain what a programming paradigm is and describe the procedural and low-level (assembly) approaches.</t>
+          <t>Describe the stages of the software development lifecycle and the outputs of each stage.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr"/>
@@ -866,7 +862,7 @@
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Apply the four addressing modes (immediate, direct, indirect, indexed) to determine the value loaded.</t>
+          <t>Compare the merits and drawbacks of Waterfall, Agile, Extreme Programming, Spiral and RAD.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr"/>
@@ -877,7 +873,7 @@
       <c r="A30" s="4" t="inlineStr"/>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Define the key object-oriented concepts and apply inheritance and polymorphism to a scenario.</t>
+          <t>Select and justify a methodology for a given scenario using explicit scenario clues.</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr"/>
@@ -885,36 +881,36 @@
       <c r="E30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>1.3.1</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Compression, Encryption and Hashing</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Write and follow algorithms, and design test data using normal, boundary and erroneous values.</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr"/>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Compare lossy and lossless compression and explain how run length encoding (RLE) and dictionary compression reduce file size.</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>1.2.4</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Types of Programming Language</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Distinguish symmetric and asymmetric encryption and explain how asymmetric encryption solves the key-distribution problem.</t>
+          <t>Explain the need for programming paradigms and characterise procedural and object-oriented programming.</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr"/>
@@ -925,7 +921,7 @@
       <c r="A34" s="4" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Explain what hashing is, its key properties and why hashing (not encryption) is used to store passwords.</t>
+          <t>Write and trace short Little Man Computer programs using the standard instruction set.</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr"/>
@@ -933,25 +929,21 @@
       <c r="E34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>1.3.2</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Databases</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Determine the value used by an instruction under immediate, direct, indirect and indexed addressing.</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr"/>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Compare flat file and relational databases and identify primary, foreign, composite and secondary keys.</t>
+          <t>Define and apply class, object, method, attribute, inheritance, encapsulation and polymorphism.</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr"/>
@@ -959,21 +951,25 @@
       <c r="E36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Apply normalisation to 1NF, 2NF and 3NF and explain the dependency removed at each stage.</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Compression, Encryption and Hashing</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Write SQL queries and explain transactions, ACID properties and record locking.</t>
+          <t>Explain why files are compressed and compare lossy with lossless compression for given scenarios.</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
@@ -981,25 +977,21 @@
       <c r="E38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>1.3.3</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Networks</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Encode and decode data using run length encoding and dictionary coding, and evaluate the saving.</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Compare LANs and WANs, client-server and peer-to-peer networks, and star and mesh topologies.</t>
+          <t>Compare symmetric and asymmetric encryption, including keys, speed and the key distribution problem.</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
@@ -1010,7 +1002,7 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Explain packet vs circuit switching, the role of DNS, and the four layers of the TCP/IP stack.</t>
+          <t>Describe the properties of hashing and justify its use for passwords and fast lookup.</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr"/>
@@ -1018,36 +1010,36 @@
       <c r="E41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr"/>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Describe the function of network hardware and security measures including switches, routers, firewalls and proxies.</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>1.3.2</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Databases</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>1.3.4</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Web Technologies</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>I can define entity, attribute and record, and compare flat file and relational databases.</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr"/>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Explain the roles of HTML, CSS and JavaScript and how CSS selectors target tags, classes and ids.</t>
+          <t>I can identify primary, foreign, composite and secondary keys and draw ER diagrams, resolving many-to-many relationships.</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
@@ -1058,7 +1050,7 @@
       <c r="A45" s="4" t="inlineStr"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Describe how search engines index pages and how the PageRank algorithm ranks them.</t>
+          <t>I can normalise a table to 3NF, naming the dependency removed at each stage.</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr"/>
@@ -1069,7 +1061,7 @@
       <c r="A46" s="4" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Compare client-side and server-side processing and justify where each should be used.</t>
+          <t>I can write and interpret SQL, and explain referential integrity, transactions, ACID and record locking.</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr"/>
@@ -1079,12 +1071,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.3.3</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Data Types</t>
+          <t>Networks</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr"/>
@@ -1095,7 +1087,7 @@
       <c r="A48" s="4" t="inlineStr"/>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Convert confidently between denary, binary and hexadecimal, and represent signed integers using two's complement.</t>
+          <t>I can compare LANs and WANs, and client-server and peer-to-peer models, with examples and trade-offs.</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr"/>
@@ -1106,7 +1098,7 @@
       <c r="A49" s="4" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Apply binary addition, subtraction and logical/arithmetic shifts, identifying overflow and the arithmetic effect of each shift.</t>
+          <t>I can explain the purpose of protocols and standards and describe the role of each TCP/IP layer, including encapsulation.</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr"/>
@@ -1117,7 +1109,7 @@
       <c r="A50" s="4" t="inlineStr"/>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Explain floating-point representation (mantissa and exponent), normalisation, and how character sets such as ASCII and Unicode encode characters.</t>
+          <t>I can describe how DNS resolves a domain name to an IP address, including the hierarchy and caching.</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr"/>
@@ -1125,36 +1117,36 @@
       <c r="E50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>1.4.2</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Data Structures</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>I can compare packet and circuit switching and state the function of key network hardware.</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr"/>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Describe and distinguish static and dynamic data structures, including arrays, records, lists, tuples and linked lists.</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>1.3.4</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Web Technologies (part 1)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Trace operations on stacks and queues, and explain their LIFO/FIFO behaviour and real-world uses.</t>
+          <t>I can describe how a browser requests a page from a web server and the roles of HTML, CSS and JavaScript.</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr"/>
@@ -1165,7 +1157,7 @@
       <c r="A54" s="4" t="inlineStr"/>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Explain how graphs, trees, binary search trees and hash tables store and retrieve data, including traversal order and collisions.</t>
+          <t>I can write and interpret HTML using the tags and attributes OCR names, correctly nested.</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr"/>
@@ -1173,25 +1165,21 @@
       <c r="E54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>1.4.3</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Boolean Algebra</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>I can style a page with CSS element, class and id selectors placed inline, internally or in an external stylesheet.</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr"/>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Construct truth tables for logic gates and combined expressions, including AND, OR, XOR, NAND and NOR.</t>
+          <t>I can write simple JavaScript including form validation, and compare client-side with server-side processing.</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr"/>
@@ -1199,21 +1187,25 @@
       <c r="E56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr"/>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Simplify Boolean expressions using identities, De Morgan's laws and Karnaugh maps.</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr"/>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>1.4.1</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Data Types</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Describe the operation of half adders, full adders and D-type flip-flops, distinguishing combinational and sequential logic.</t>
+          <t>Convert confidently between denary, binary and hexadecimal, and represent signed integers using two's complement.</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
@@ -1221,25 +1213,21 @@
       <c r="E58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Computing Related Legislation</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Apply binary addition, subtraction and logical/arithmetic shifts, identifying overflow and the arithmetic effect of each shift.</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr"/>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Identify and describe the four key Acts: the Data Protection Act 1998/2018 (with GDPR), the Computer Misuse Act 1990, the Copyright, Designs &amp; Patents Act 1988 and the Regulation of Investigatory Powers Act 2000.</t>
+          <t>Explain floating-point representation (mantissa and exponent), normalisation, and how character sets such as ASCII and Unicode encode characters.</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
@@ -1247,21 +1235,25 @@
       <c r="E60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr"/>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>Select the correct law (and Computer Misuse Act offence) that applies to a given computing scenario, naming the responsible party.</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="4" t="inlineStr"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>1.4.2</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr"/>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Explain why more than one law can apply to a single scenario, distinguishing between the wrongdoing of each party involved.</t>
+          <t>Describe and distinguish static and dynamic data structures, including arrays, records, lists, tuples and linked lists.</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr"/>
@@ -1269,25 +1261,21 @@
       <c r="E62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>1.5.2</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Moral and Ethical Issues</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Trace operations on stacks and queues, and explain their LIFO/FIFO behaviour and real-world uses.</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Describe the key moral, ethical, cultural and social issues raised by computing, identifying both a benefit and a drawback for each.</t>
+          <t>Explain how graphs, trees, binary search trees and hash tables store and retrieve data, including traversal order and collisions.</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr"/>
@@ -1295,21 +1283,25 @@
       <c r="E64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr"/>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Identify the stakeholders affected by a computing decision and explain how the same fact can benefit one group while harming another.</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr"/>
-      <c r="D65" s="4" t="inlineStr"/>
-      <c r="E65" s="4" t="inlineStr"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>1.4.3</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Boolean Algebra</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr"/>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Structure a balanced levels-of-response 'discuss' answer that weighs both sides and reaches a justified conclusion.</t>
+          <t>Construct truth tables for logic gates and combined expressions, including AND, OR, XOR, NAND and NOR.</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
@@ -1317,25 +1309,21 @@
       <c r="E66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Abstractly</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
+      <c r="A67" s="4" t="inlineStr"/>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Simplify Boolean expressions using identities, De Morgan's laws and Karnaugh maps.</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr"/>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Define abstraction as removing or hiding detail irrelevant to a problem, leaving only what is needed to solve it.</t>
+          <t>Describe the operation of half adders, full adders and D-type flip-flops, distinguishing combinational and sequential logic.</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
@@ -1343,21 +1331,25 @@
       <c r="E68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr"/>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Distinguish representational abstraction from generalisation/categorisation, and abstraction from decomposition.</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr"/>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="4" t="inlineStr"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Computing Related Legislation</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Apply abstraction to an unseen scenario by justifying which real-world details are kept and which are discarded.</t>
+          <t>Identify and describe the four key Acts: the Data Protection Act 1998/2018 (with GDPR), the Computer Misuse Act 1990, the Copyright, Designs &amp; Patents Act 1988 and the Regulation of Investigatory Powers Act 2000.</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
@@ -1365,25 +1357,21 @@
       <c r="E70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>2.1.2</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Ahead</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
+      <c r="A71" s="4" t="inlineStr"/>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Select the correct law (and Computer Misuse Act offence) that applies to a given computing scenario, naming the responsible party.</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr"/>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Identify the inputs and outputs of a routine, distinguishing them from internal processes.</t>
+          <t>Explain why more than one law can apply to a single scenario, distinguishing between the wrongdoing of each party involved.</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr"/>
@@ -1391,21 +1379,25 @@
       <c r="E72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr"/>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Explain preconditions, caching and reusable components, including the benefits and trade-offs of caching.</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>1.5.2</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Moral and Ethical Issues</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr"/>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Apply thinking ahead to plan an unseen routine before coding it.</t>
+          <t>Describe the key moral, ethical, cultural and social issues raised by computing, identifying both a benefit and a drawback for each.</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr"/>
@@ -1413,25 +1405,21 @@
       <c r="E74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>2.1.3</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Procedurally</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
+      <c r="A75" s="4" t="inlineStr"/>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Identify the stakeholders affected by a computing decision and explain how the same fact can benefit one group while harming another.</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr"/>
+      <c r="D75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Decompose a problem into named sub-procedures, each performing one task.</t>
+          <t>Structure a balanced levels-of-response 'discuss' answer that weighs both sides and reaches a justified conclusion.</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr"/>
@@ -1439,21 +1427,25 @@
       <c r="E76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr"/>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Determine the fixed order of steps by identifying data dependencies between them.</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Abstractly</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Apply procedural thinking to sequence an unseen scenario and justify why the order is fixed.</t>
+          <t>I can explain the nature and need for abstraction: removing detail irrelevant to the problem</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr"/>
@@ -1461,25 +1453,21 @@
       <c r="E78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>2.1.4</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Logically</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="A79" s="4" t="inlineStr"/>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>I can distinguish representational abstraction from generalisation, with a valid example of each</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr"/>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr"/>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Identify decision points where the flow of control branches on a condition.</t>
+          <t>I can compare an abstraction with reality and justify which details are kept or discarded for a purpose</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr"/>
@@ -1490,7 +1478,7 @@
       <c r="A81" s="4" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Write exact Boolean conditions, including the correct comparison operator and logical operators.</t>
+          <t>I can devise an abstract model for a given real-world scenario</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr"/>
@@ -1498,36 +1486,36 @@
       <c r="E81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr"/>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Apply logical thinking to an unseen scenario, stating the outcome of both branches of each decision.</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr"/>
-      <c r="D82" s="4" t="inlineStr"/>
-      <c r="E82" s="4" t="inlineStr"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Ahead</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>2.1.5</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Concurrently</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
+      <c r="A83" s="4" t="inlineStr"/>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>I can identify the inputs and outputs of a routine, distinguishing them from internal processes.</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Identify tasks that can run concurrently because they have no data dependency.</t>
+          <t>I can state preconditions for a routine and explain the consequences of not meeting them.</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr"/>
@@ -1538,7 +1526,7 @@
       <c r="A85" s="4" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Explain the benefits and trade-offs of concurrency, including race conditions and deadlock.</t>
+          <t>I can explain caching and prefetching, pairing each benefit with its trade-off.</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr"/>
@@ -1549,7 +1537,7 @@
       <c r="A86" s="4" t="inlineStr"/>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Apply concurrent thinking to an unseen scenario, weighing one benefit against one trade-off.</t>
+          <t>I can justify the use of reusable program components in a given scenario.</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr"/>
@@ -1559,12 +1547,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.1.3</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Programming Techniques</t>
+          <t>Thinking Procedurally</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr"/>
@@ -1575,7 +1563,7 @@
       <c r="A88" s="4" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Describe and distinguish the programming constructs (sequence, selection, count- and condition-controlled iteration), recursion, scope, modularity and OOP</t>
+          <t>Identify the components of a problem and decompose it into smaller sub-problems.</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr"/>
@@ -1586,7 +1574,7 @@
       <c r="A89" s="4" t="inlineStr"/>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Explain how recursion uses a base case and a call stack of frames, and contrast it with iteration</t>
+          <t>Identify the components of a solution as named sub-procedures, each doing one clear job.</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr"/>
@@ -1597,7 +1585,7 @@
       <c r="A90" s="4" t="inlineStr"/>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Apply scope rules, parameter passing (by value vs by reference) and OOP concepts (encapsulation, inheritance, polymorphism) when reading and writing OCR pseudocode</t>
+          <t>Determine and justify the order of steps needed to solve a problem using data dependencies.</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr"/>
@@ -1605,36 +1593,36 @@
       <c r="E90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>2.2.2</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Computational Methods</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr"/>
-      <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
+      <c r="A91" s="4" t="inlineStr"/>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Explain the benefits of a modular, procedural solution for building, testing and maintenance.</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr"/>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr"/>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>State the features that make a problem solvable computationally and recognise non-computable and intractable problems</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Logically</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Describe problem recognition, decomposition, divide and conquer, and abstraction (representational and by generalisation)</t>
+          <t>Identify the points in a problem or program where a decision has to be taken.</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr"/>
@@ -1645,7 +1633,7 @@
       <c r="A94" s="4" t="inlineStr"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Apply named computational methods (backtracking, data mining, heuristics, performance modelling, pipelining, visualisation) to suitable problems, justifying why each fits</t>
+          <t>Determine the exact Boolean conditions, using comparison and logical operators, that affect each decision's outcome.</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr"/>
@@ -1653,25 +1641,21 @@
       <c r="E94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>2.3.1</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Algorithms</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr"/>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="inlineStr"/>
+      <c r="A95" s="4" t="inlineStr"/>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Explain how decisions determine the flow of control through selection and iteration, stating both branches.</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr"/>
+      <c r="D95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr"/>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Use Big O notation to express and justify the time and space complexity of an algorithm, simplifying expressions to the dominant term.</t>
+          <t>Verify the logical flow of a routine using a trace table and correct common logic errors.</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr"/>
@@ -1679,68 +1663,238 @@
       <c r="E96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr"/>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Compare standard searching and sorting algorithms by how they work and their best, average and worst-case complexities.</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="inlineStr"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2.1.5</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Concurrently</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr"/>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Describe and trace algorithms on data structures, including tree traversals and the shortest-path algorithms Dijkstra and A*.</t>
+          <t>Identify tasks that can run concurrently because they have no data dependency.</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr"/>
       <c r="D98" s="4" t="inlineStr"/>
       <c r="E98" s="4" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Explain the benefits and trade-offs of concurrency, including race conditions and deadlock.</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr"/>
+      <c r="D99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr"/>
+    </row>
     <row r="100">
-      <c r="B100" s="6" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr"/>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Apply concurrent thinking to an unseen scenario, weighing one benefit against one trade-off.</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Programming Techniques</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr"/>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Describe and distinguish the programming constructs (sequence, selection, count- and condition-controlled iteration), recursion, scope, modularity and OOP</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr"/>
+      <c r="D102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr"/>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Explain how recursion uses a base case and a call stack of frames, and contrast it with iteration</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr"/>
+      <c r="D103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr"/>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Apply scope rules, parameter passing (by value vs by reference) and OOP concepts (encapsulation, inheritance, polymorphism) when reading and writing OCR pseudocode</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2.2.2</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Computational Methods</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr"/>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr"/>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>State the features that make a problem solvable computationally and recognise non-computable and intractable problems</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr"/>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Describe problem recognition, decomposition, divide and conquer, and abstraction (representational and by generalisation)</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr"/>
+      <c r="D107" s="4" t="inlineStr"/>
+      <c r="E107" s="4" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr"/>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Apply named computational methods (backtracking, data mining, heuristics, performance modelling, pipelining, visualisation) to suitable problems, justifying why each fits</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr"/>
+      <c r="D108" s="4" t="inlineStr"/>
+      <c r="E108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Algorithms</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr"/>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr"/>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Use Big O notation to express and justify the time and space complexity of an algorithm, simplifying expressions to the dominant term.</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr"/>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Compare standard searching and sorting algorithms by how they work and their best, average and worst-case complexities.</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr"/>
+      <c r="D111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr"/>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Describe and trace algorithms on data structures, including tree traversals and the shortest-path algorithms Dijkstra and A*.</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr"/>
+      <c r="D112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>🔴 Not yet (R):</t>
         </is>
       </c>
-      <c r="C100">
-        <f>COUNTIF(C2:C98,"R")</f>
+      <c r="C114">
+        <f>COUNTIF(C2:C112,"R")</f>
         <v/>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="6" t="inlineStr">
+    <row r="115">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>🟠 Getting there (A):</t>
         </is>
       </c>
-      <c r="C101">
-        <f>COUNTIF(C2:C98,"A")</f>
+      <c r="C115">
+        <f>COUNTIF(C2:C112,"A")</f>
         <v/>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="6" t="inlineStr">
+    <row r="116">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>🟢 Confident (G):</t>
         </is>
       </c>
-      <c r="C102">
-        <f>COUNTIF(C2:C98,"G")</f>
+      <c r="C116">
+        <f>COUNTIF(C2:C112,"G")</f>
         <v/>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" s="7" t="inlineStr">
+    <row r="117">
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>Total objectives:</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>73</v>
+      <c r="C117" t="n">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1821,7 +1975,7 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
+  <conditionalFormatting sqref="C11">
     <cfRule type="cellIs" priority="22" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -1854,18 +2008,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="cellIs" priority="31" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="32" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="33" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C17">
     <cfRule type="cellIs" priority="34" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -1887,29 +2041,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="cellIs" priority="40" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="41" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C20">
-    <cfRule type="cellIs" priority="40" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="41" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="42" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="43" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="44" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="45" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21">
-    <cfRule type="cellIs" priority="43" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="44" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="45" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C22">
     <cfRule type="cellIs" priority="46" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -1920,73 +2074,73 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C23">
+    <cfRule type="cellIs" priority="49" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="50" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="51" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C24">
-    <cfRule type="cellIs" priority="49" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="50" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="51" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="52" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="53" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="54" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25">
-    <cfRule type="cellIs" priority="52" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="53" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="54" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="55" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="56" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="57" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26">
-    <cfRule type="cellIs" priority="55" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="56" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="57" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="58" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="59" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="60" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28">
-    <cfRule type="cellIs" priority="58" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="59" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="60" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="61" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="62" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="63" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29">
-    <cfRule type="cellIs" priority="61" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="62" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="63" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="64" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="65" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="66" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30">
-    <cfRule type="cellIs" priority="64" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="65" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="66" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C32">
     <cfRule type="cellIs" priority="67" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -1997,558 +2151,712 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C31">
+    <cfRule type="cellIs" priority="70" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="71" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="72" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C33">
-    <cfRule type="cellIs" priority="70" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="71" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="72" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="73" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="74" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="75" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C34">
-    <cfRule type="cellIs" priority="73" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="74" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="75" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="76" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="77" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="78" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C35">
+    <cfRule type="cellIs" priority="79" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="80" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="81" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36">
-    <cfRule type="cellIs" priority="76" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="77" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="78" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C37">
-    <cfRule type="cellIs" priority="79" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="80" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="81" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="82" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="83" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="84" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C38">
-    <cfRule type="cellIs" priority="82" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="83" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="84" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="85" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="86" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="87" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39">
+    <cfRule type="cellIs" priority="88" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="89" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="90" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C40">
-    <cfRule type="cellIs" priority="85" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="86" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="87" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="91" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="92" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="93" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41">
-    <cfRule type="cellIs" priority="88" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="89" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="90" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C42">
-    <cfRule type="cellIs" priority="91" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="92" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="93" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="94" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="95" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="96" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C43">
+    <cfRule type="cellIs" priority="97" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="98" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="99" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C44">
-    <cfRule type="cellIs" priority="94" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="95" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="96" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="100" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="101" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="102" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45">
-    <cfRule type="cellIs" priority="97" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="98" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="99" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="103" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="104" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="105" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46">
-    <cfRule type="cellIs" priority="100" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="101" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="102" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="106" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="107" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="108" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48">
-    <cfRule type="cellIs" priority="103" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="104" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="105" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="109" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="110" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="111" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C49">
-    <cfRule type="cellIs" priority="106" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="107" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="108" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="112" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="113" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="114" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C50">
-    <cfRule type="cellIs" priority="109" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="110" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="111" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C52">
-    <cfRule type="cellIs" priority="112" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="113" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="114" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="115" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="116" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="117" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C51">
+    <cfRule type="cellIs" priority="118" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="119" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="120" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C53">
-    <cfRule type="cellIs" priority="115" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="116" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="117" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="121" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="122" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="123" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
-    <cfRule type="cellIs" priority="118" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="119" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="120" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="124" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="125" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="126" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C55">
+    <cfRule type="cellIs" priority="127" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="128" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="129" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C56">
-    <cfRule type="cellIs" priority="121" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="122" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="123" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C57">
-    <cfRule type="cellIs" priority="124" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="125" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="126" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="130" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="131" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="132" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C58">
-    <cfRule type="cellIs" priority="127" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="128" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="129" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="133" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="134" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="135" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C59">
+    <cfRule type="cellIs" priority="136" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="137" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="138" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60">
-    <cfRule type="cellIs" priority="130" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="131" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="132" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C61">
-    <cfRule type="cellIs" priority="133" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="134" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="135" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="139" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="140" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="141" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C62">
-    <cfRule type="cellIs" priority="136" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="137" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="138" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="142" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="143" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="144" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C63">
+    <cfRule type="cellIs" priority="145" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="146" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="147" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C64">
-    <cfRule type="cellIs" priority="139" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="140" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="141" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C65">
-    <cfRule type="cellIs" priority="142" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="143" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="144" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="148" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="149" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="150" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C66">
-    <cfRule type="cellIs" priority="145" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="146" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="147" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="151" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="152" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="153" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C67">
+    <cfRule type="cellIs" priority="154" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="155" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="156" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C68">
-    <cfRule type="cellIs" priority="148" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="149" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="150" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C69">
-    <cfRule type="cellIs" priority="151" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="152" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="153" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="157" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="158" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="159" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C70">
-    <cfRule type="cellIs" priority="154" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="155" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="156" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="160" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="161" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="162" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C71">
+    <cfRule type="cellIs" priority="163" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="164" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="165" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C72">
-    <cfRule type="cellIs" priority="157" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="158" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="159" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C73">
-    <cfRule type="cellIs" priority="160" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="161" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="162" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="166" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="167" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="168" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C74">
-    <cfRule type="cellIs" priority="163" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="164" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="165" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="169" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="170" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="171" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C75">
+    <cfRule type="cellIs" priority="172" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="173" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="174" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C76">
-    <cfRule type="cellIs" priority="166" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="167" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="168" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
-    <cfRule type="cellIs" priority="169" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="170" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="171" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="175" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="176" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="177" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="cellIs" priority="172" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="173" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="174" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="178" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="179" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="180" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C79">
+    <cfRule type="cellIs" priority="181" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="182" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="183" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C80">
-    <cfRule type="cellIs" priority="175" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="176" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="177" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="184" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="185" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="186" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C81">
-    <cfRule type="cellIs" priority="178" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="179" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="180" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C82">
-    <cfRule type="cellIs" priority="181" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="182" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="183" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="187" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="188" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="189" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C83">
+    <cfRule type="cellIs" priority="190" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="191" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="192" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C84">
-    <cfRule type="cellIs" priority="184" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="185" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="186" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="193" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="194" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="195" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C85">
-    <cfRule type="cellIs" priority="187" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="188" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="189" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="196" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="197" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="198" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C86">
-    <cfRule type="cellIs" priority="190" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="191" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="192" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="199" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="200" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="201" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C88">
-    <cfRule type="cellIs" priority="193" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="194" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="195" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="202" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="203" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="204" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C89">
-    <cfRule type="cellIs" priority="196" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="197" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="198" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="205" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="206" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="207" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C90">
-    <cfRule type="cellIs" priority="199" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="200" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="201" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C92">
-    <cfRule type="cellIs" priority="202" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="203" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="204" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="208" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="209" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="210" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C91">
+    <cfRule type="cellIs" priority="211" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="212" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="213" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="cellIs" priority="205" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="206" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="207" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="214" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="215" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="216" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C94">
-    <cfRule type="cellIs" priority="208" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="209" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="210" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="217" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="218" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="219" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C95">
+    <cfRule type="cellIs" priority="220" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="221" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="222" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C96">
-    <cfRule type="cellIs" priority="211" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="212" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="213" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C97">
-    <cfRule type="cellIs" priority="214" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="215" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="216" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="223" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="224" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="225" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="cellIs" priority="217" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="218" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="219" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="226" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="227" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="228" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C99">
+    <cfRule type="cellIs" priority="229" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="230" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="231" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C100">
+    <cfRule type="cellIs" priority="232" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="233" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="234" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C102">
+    <cfRule type="cellIs" priority="235" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="236" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="237" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C103">
+    <cfRule type="cellIs" priority="238" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="239" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="240" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C104">
+    <cfRule type="cellIs" priority="241" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="242" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="243" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C106">
+    <cfRule type="cellIs" priority="244" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="245" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="246" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C107">
+    <cfRule type="cellIs" priority="247" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="248" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="249" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C108">
+    <cfRule type="cellIs" priority="250" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="251" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="252" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C110">
+    <cfRule type="cellIs" priority="253" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="254" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="255" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C111">
+    <cfRule type="cellIs" priority="256" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="257" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="258" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C112">
+    <cfRule type="cellIs" priority="259" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="260" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="261" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C3 C4 C5 C6 C8 C9 C10 C12 C13 C14 C16 C17 C18 C20 C21 C22 C24 C25 C26 C28 C29 C30 C32 C33 C34 C36 C37 C38 C40 C41 C42 C44 C45 C46 C48 C49 C50 C52 C53 C54 C56 C57 C58 C60 C61 C62 C64 C65 C66 C68 C69 C70 C72 C73 C74 C76 C77 C78 C80 C81 C82 C84 C85 C86 C88 C89 C90 C92 C93 C94 C96 C97 C98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="R = not yet, A = getting there, G = confident" type="list">
+    <dataValidation sqref="C3 C4 C5 C6 C8 C9 C10 C11 C13 C14 C15 C16 C18 C19 C20 C21 C23 C24 C25 C26 C28 C29 C30 C31 C33 C34 C35 C36 C38 C39 C40 C41 C43 C44 C45 C46 C48 C49 C50 C51 C53 C54 C55 C56 C58 C59 C60 C62 C63 C64 C66 C67 C68 C70 C71 C72 C74 C75 C76 C78 C79 C80 C81 C83 C84 C85 C86 C88 C89 C90 C91 C93 C94 C95 C96 C98 C99 C100 C102 C103 C104 C106 C107 C108 C110 C111 C112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="R = not yet, A = getting there, G = confident" type="list">
       <formula1>"R,A,G"</formula1>
     </dataValidation>
   </dataValidations>

--- a/0 Planning/Personal Learning Checklist.xlsx
+++ b/0 Planning/Personal Learning Checklist.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Data Types</t>
+          <t>Data Types (part 1)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       <c r="A58" s="4" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Convert confidently between denary, binary and hexadecimal, and represent signed integers using two's complement.</t>
+          <t>I can choose and justify the correct primitive data type (integer, real, char, string, Boolean) for given data.</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       <c r="A59" s="4" t="inlineStr"/>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Apply binary addition, subtraction and logical/arithmetic shifts, identifying overflow and the arithmetic effect of each shift.</t>
+          <t>I can convert between denary, binary and hexadecimal in all six directions, showing my working.</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr"/>
@@ -1227,7 +1227,7 @@
       <c r="A60" s="4" t="inlineStr"/>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Explain floating-point representation (mantissa and exponent), normalisation, and how character sets such as ASCII and Unicode encode characters.</t>
+          <t>I can add binary numbers, carry correctly, and recognise when overflow has occurred.</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr"/>
@@ -1235,36 +1235,36 @@
       <c r="E60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>I can represent negative integers in sign and magnitude and two's complement, and subtract by adding a two's complement.</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>1.4.2</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Data Structures</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr"/>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Describe and distinguish static and dynamic data structures, including arrays, records, lists, tuples and linked lists.</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="4" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures (part 1)</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr"/>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Trace operations on stacks and queues, and explain their LIFO/FIFO behaviour and real-world uses.</t>
+          <t>I can describe arrays (1D, 2D and 3D), records, lists and tuples, and choose the right one for given data.</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
       <c r="A64" s="4" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Explain how graphs, trees, binary search trees and hash tables store and retrieve data, including traversal order and collisions.</t>
+          <t>I can use index arithmetic to locate an element in a 1D or 2D array.</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr"/>
@@ -1283,25 +1283,21 @@
       <c r="E64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>1.4.3</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Boolean Algebra</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="A65" s="4" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>I can trace push, pop and peek on a stack using a stack pointer, and identify overflow and underflow.</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr"/>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Construct truth tables for logic gates and combined expressions, including AND, OR, XOR, NAND and NOR.</t>
+          <t>I can trace enqueue and dequeue on linear and circular queues and explain why circular queues reuse space.</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr"/>
@@ -1309,21 +1305,25 @@
       <c r="E66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr"/>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Simplify Boolean expressions using identities, De Morgan's laws and Karnaugh maps.</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr"/>
-      <c r="D67" s="4" t="inlineStr"/>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>1.4.3</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Boolean Algebra (part 1)</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr"/>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Describe the operation of half adders, full adders and D-type flip-flops, distinguishing combinational and sequential logic.</t>
+          <t>I can state the truth tables for AND, OR, NOT and XOR and recognise their circuit symbols.</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr"/>
@@ -1331,25 +1331,21 @@
       <c r="E68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>1.5.1</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Computing Related Legislation</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="A69" s="4" t="inlineStr"/>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>I can combine gates into circuits and construct truth tables for 2- and 3-input expressions using working columns.</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Identify and describe the four key Acts: the Data Protection Act 1998/2018 (with GDPR), the Computer Misuse Act 1990, the Copyright, Designs &amp; Patents Act 1988 and the Regulation of Investigatory Powers Act 2000.</t>
+          <t>I can state and apply the Boolean identities: commutation, association, distribution, absorption and double negation.</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr"/>
@@ -1360,7 +1356,7 @@
       <c r="A71" s="4" t="inlineStr"/>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Select the correct law (and Computer Misuse Act offence) that applies to a given computing scenario, naming the responsible party.</t>
+          <t>I can apply De Morgan's laws and simplify Boolean expressions, naming the law used at each step.</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr"/>
@@ -1368,36 +1364,36 @@
       <c r="E71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Explain why more than one law can apply to a single scenario, distinguishing between the wrongdoing of each party involved.</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr"/>
-      <c r="D72" s="4" t="inlineStr"/>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>1.5.1</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Computing Related Legislation</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>1.5.2</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Moral and Ethical Issues</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
+      <c r="A73" s="4" t="inlineStr"/>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Identify and describe the four key Acts: the Data Protection Act 1998/2018 (with GDPR), the Computer Misuse Act 1990, the Copyright, Designs &amp; Patents Act 1988 and the Regulation of Investigatory Powers Act 2000.</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr"/>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Describe the key moral, ethical, cultural and social issues raised by computing, identifying both a benefit and a drawback for each.</t>
+          <t>Select the correct law (and Computer Misuse Act offence) that applies to a given computing scenario, naming the responsible party.</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr"/>
@@ -1408,7 +1404,7 @@
       <c r="A75" s="4" t="inlineStr"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Identify the stakeholders affected by a computing decision and explain how the same fact can benefit one group while harming another.</t>
+          <t>Explain why more than one law can apply to a single scenario, distinguishing between the wrongdoing of each party involved.</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr"/>
@@ -1416,36 +1412,36 @@
       <c r="E75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr"/>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Structure a balanced levels-of-response 'discuss' answer that weighs both sides and reaches a justified conclusion.</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr"/>
-      <c r="D76" s="4" t="inlineStr"/>
-      <c r="E76" s="4" t="inlineStr"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>1.5.2</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Moral and Ethical Issues</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Abstractly</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="A77" s="4" t="inlineStr"/>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Describe the key moral, ethical, cultural and social issues raised by computing, identifying both a benefit and a drawback for each.</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>I can explain the nature and need for abstraction: removing detail irrelevant to the problem</t>
+          <t>Identify the stakeholders affected by a computing decision and explain how the same fact can benefit one group while harming another.</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr"/>
@@ -1456,7 +1452,7 @@
       <c r="A79" s="4" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>I can distinguish representational abstraction from generalisation, with a valid example of each</t>
+          <t>Structure a balanced levels-of-response 'discuss' answer that weighs both sides and reaches a justified conclusion.</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr"/>
@@ -1464,21 +1460,25 @@
       <c r="E79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr"/>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>I can compare an abstraction with reality and justify which details are kept or discarded for a purpose</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Abstractly</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>I can devise an abstract model for a given real-world scenario</t>
+          <t>I can explain the nature and need for abstraction: removing detail irrelevant to the problem</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr"/>
@@ -1486,25 +1486,21 @@
       <c r="E81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>2.1.2</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Ahead</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="A82" s="4" t="inlineStr"/>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>I can distinguish representational abstraction from generalisation, with a valid example of each</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr"/>
+      <c r="D82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr"/>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>I can identify the inputs and outputs of a routine, distinguishing them from internal processes.</t>
+          <t>I can compare an abstraction with reality and justify which details are kept or discarded for a purpose</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr"/>
@@ -1515,7 +1511,7 @@
       <c r="A84" s="4" t="inlineStr"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>I can state preconditions for a routine and explain the consequences of not meeting them.</t>
+          <t>I can devise an abstract model for a given real-world scenario</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr"/>
@@ -1523,21 +1519,25 @@
       <c r="E84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr"/>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>I can explain caching and prefetching, pairing each benefit with its trade-off.</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr"/>
-      <c r="D85" s="4" t="inlineStr"/>
-      <c r="E85" s="4" t="inlineStr"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Ahead</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr"/>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>I can justify the use of reusable program components in a given scenario.</t>
+          <t>I can identify the inputs and outputs of a routine, distinguishing them from internal processes.</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr"/>
@@ -1545,25 +1545,21 @@
       <c r="E86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>2.1.3</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Procedurally</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr"/>
-      <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="2" t="inlineStr"/>
+      <c r="A87" s="4" t="inlineStr"/>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>I can state preconditions for a routine and explain the consequences of not meeting them.</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr"/>
+      <c r="D87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Identify the components of a problem and decompose it into smaller sub-problems.</t>
+          <t>I can explain caching and prefetching, pairing each benefit with its trade-off.</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr"/>
@@ -1574,7 +1570,7 @@
       <c r="A89" s="4" t="inlineStr"/>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Identify the components of a solution as named sub-procedures, each doing one clear job.</t>
+          <t>I can justify the use of reusable program components in a given scenario.</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr"/>
@@ -1582,21 +1578,25 @@
       <c r="E89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr"/>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Determine and justify the order of steps needed to solve a problem using data dependencies.</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr"/>
-      <c r="D90" s="4" t="inlineStr"/>
-      <c r="E90" s="4" t="inlineStr"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2.1.3</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Procedurally</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Explain the benefits of a modular, procedural solution for building, testing and maintenance.</t>
+          <t>Identify the components of a problem and decompose it into smaller sub-problems.</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr"/>
@@ -1604,25 +1604,21 @@
       <c r="E91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>2.1.4</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Logically</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="2" t="inlineStr"/>
+      <c r="A92" s="4" t="inlineStr"/>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Identify the components of a solution as named sub-procedures, each doing one clear job.</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr"/>
+      <c r="D92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Identify the points in a problem or program where a decision has to be taken.</t>
+          <t>Determine and justify the order of steps needed to solve a problem using data dependencies.</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr"/>
@@ -1633,7 +1629,7 @@
       <c r="A94" s="4" t="inlineStr"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Determine the exact Boolean conditions, using comparison and logical operators, that affect each decision's outcome.</t>
+          <t>Explain the benefits of a modular, procedural solution for building, testing and maintenance.</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr"/>
@@ -1641,21 +1637,25 @@
       <c r="E94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr"/>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Explain how decisions determine the flow of control through selection and iteration, stating both branches.</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr"/>
-      <c r="D95" s="4" t="inlineStr"/>
-      <c r="E95" s="4" t="inlineStr"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Logically</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr"/>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Verify the logical flow of a routine using a trace table and correct common logic errors.</t>
+          <t>Identify the points in a problem or program where a decision has to be taken.</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr"/>
@@ -1663,25 +1663,21 @@
       <c r="E96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>2.1.5</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Concurrently</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr"/>
-      <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="A97" s="4" t="inlineStr"/>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Determine the exact Boolean conditions, using comparison and logical operators, that affect each decision's outcome.</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr"/>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Identify tasks that can run concurrently because they have no data dependency.</t>
+          <t>Explain how decisions determine the flow of control through selection and iteration, stating both branches.</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr"/>
@@ -1692,7 +1688,7 @@
       <c r="A99" s="4" t="inlineStr"/>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Explain the benefits and trade-offs of concurrency, including race conditions and deadlock.</t>
+          <t>Verify the logical flow of a routine using a trace table and correct common logic errors.</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr"/>
@@ -1700,36 +1696,36 @@
       <c r="E99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr"/>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Apply concurrent thinking to an unseen scenario, weighing one benefit against one trade-off.</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr"/>
-      <c r="D100" s="4" t="inlineStr"/>
-      <c r="E100" s="4" t="inlineStr"/>
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2.1.5</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Concurrently</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Programming Techniques</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr"/>
-      <c r="D101" s="2" t="inlineStr"/>
-      <c r="E101" s="2" t="inlineStr"/>
+      <c r="A101" s="4" t="inlineStr"/>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>I can explain what it means for parts of a problem to be carried out concurrently.</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr"/>
+      <c r="D101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr"/>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Describe and distinguish the programming constructs (sequence, selection, count- and condition-controlled iteration), recursion, scope, modularity and OOP</t>
+          <t>I can identify which tasks in a scenario can run at the same time by checking for data dependencies.</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr"/>
@@ -1740,7 +1736,7 @@
       <c r="A103" s="4" t="inlineStr"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Explain how recursion uses a base case and a call stack of frames, and contrast it with iteration</t>
+          <t>I can weigh the benefits of concurrency (speed, responsiveness, hardware use) against its trade-offs (shared data, coordination, testing).</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr"/>
@@ -1751,7 +1747,7 @@
       <c r="A104" s="4" t="inlineStr"/>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Apply scope rules, parameter passing (by value vs by reference) and OOP concepts (encapsulation, inheritance, polymorphism) when reading and writing OCR pseudocode</t>
+          <t>I can distinguish true parallel processing on multiple cores from concurrency by time-slicing on one core.</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr"/>
@@ -1761,12 +1757,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Computational Methods</t>
+          <t>Programming Techniques</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr"/>
@@ -1777,7 +1773,7 @@
       <c r="A106" s="4" t="inlineStr"/>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>State the features that make a problem solvable computationally and recognise non-computable and intractable problems</t>
+          <t>I can use sequence, branching and both count- and condition-controlled iteration in OCR Exam Reference Language.</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr"/>
@@ -1788,7 +1784,7 @@
       <c r="A107" s="4" t="inlineStr"/>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Describe problem recognition, decomposition, divide and conquer, and abstraction (representational and by generalisation)</t>
+          <t>I can trace a recursive subroutine using stack frames, identify its base case, and compare recursion with iteration.</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr"/>
@@ -1799,7 +1795,7 @@
       <c r="A108" s="4" t="inlineStr"/>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Apply named computational methods (backtracking, data mining, heuristics, performance modelling, pipelining, visualisation) to suitable problems, justifying why each fits</t>
+          <t>I can explain scope, distinguish functions from procedures, and predict the effect of passing parameters by value and by reference.</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr"/>
@@ -1807,36 +1803,36 @@
       <c r="E108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>2.3.1</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Algorithms</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr"/>
-      <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="inlineStr"/>
+      <c r="A109" s="4" t="inlineStr"/>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>I can describe IDE features that help build and debug code, and apply OOP techniques: encapsulation, inheritance and polymorphism.</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr"/>
+      <c r="D109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr"/>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Use Big O notation to express and justify the time and space complexity of an algorithm, simplifying expressions to the dominant term.</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr"/>
-      <c r="D110" s="4" t="inlineStr"/>
-      <c r="E110" s="4" t="inlineStr"/>
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2.2.2</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Computational Methods</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr"/>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr"/>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Compare standard searching and sorting algorithms by how they work and their best, average and worst-case complexities.</t>
+          <t>State the features that make a problem solvable computationally and recognise non-computable and intractable problems</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr"/>
@@ -1847,54 +1843,113 @@
       <c r="A112" s="4" t="inlineStr"/>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Describe and trace algorithms on data structures, including tree traversals and the shortest-path algorithms Dijkstra and A*.</t>
+          <t>Describe problem recognition, decomposition, divide and conquer, and abstraction (representational and by generalisation)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr"/>
       <c r="D112" s="4" t="inlineStr"/>
       <c r="E112" s="4" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr"/>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Apply named computational methods (backtracking, data mining, heuristics, performance modelling, pipelining, visualisation) to suitable problems, justifying why each fits</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr"/>
+      <c r="D113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr"/>
+    </row>
     <row r="114">
-      <c r="B114" s="6" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Algorithms</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr"/>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr"/>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Use Big O notation to express and justify the time and space complexity of an algorithm, simplifying expressions to the dominant term.</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr"/>
+      <c r="D115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr"/>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Compare standard searching and sorting algorithms by how they work and their best, average and worst-case complexities.</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr"/>
+      <c r="D116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr"/>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Describe and trace algorithms on data structures, including tree traversals and the shortest-path algorithms Dijkstra and A*.</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr"/>
+      <c r="D117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>🔴 Not yet (R):</t>
         </is>
       </c>
-      <c r="C114">
-        <f>COUNTIF(C2:C112,"R")</f>
+      <c r="C119">
+        <f>COUNTIF(C2:C117,"R")</f>
         <v/>
       </c>
     </row>
-    <row r="115">
-      <c r="B115" s="6" t="inlineStr">
+    <row r="120">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>🟠 Getting there (A):</t>
         </is>
       </c>
-      <c r="C115">
-        <f>COUNTIF(C2:C112,"A")</f>
+      <c r="C120">
+        <f>COUNTIF(C2:C117,"A")</f>
         <v/>
       </c>
     </row>
-    <row r="116">
-      <c r="B116" s="6" t="inlineStr">
+    <row r="121">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>🟢 Confident (G):</t>
         </is>
       </c>
-      <c r="C116">
-        <f>COUNTIF(C2:C112,"G")</f>
+      <c r="C121">
+        <f>COUNTIF(C2:C117,"G")</f>
         <v/>
       </c>
     </row>
-    <row r="117">
-      <c r="B117" s="7" t="inlineStr">
+    <row r="122">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>Total objectives:</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>87</v>
+      <c r="C122" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2415,7 +2470,7 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C62">
+  <conditionalFormatting sqref="C61">
     <cfRule type="cellIs" priority="142" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2448,18 +2503,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C65">
+    <cfRule type="cellIs" priority="151" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="152" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="153" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C66">
-    <cfRule type="cellIs" priority="151" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="152" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="153" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C67">
     <cfRule type="cellIs" priority="154" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2481,29 +2536,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C69">
+    <cfRule type="cellIs" priority="160" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="161" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="162" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C70">
-    <cfRule type="cellIs" priority="160" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="161" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="162" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="163" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="164" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="165" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C71">
-    <cfRule type="cellIs" priority="163" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="164" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="165" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C72">
     <cfRule type="cellIs" priority="166" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2514,29 +2569,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C73">
+    <cfRule type="cellIs" priority="169" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="170" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="171" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C74">
-    <cfRule type="cellIs" priority="169" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="170" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="171" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="172" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="173" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="174" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C75">
-    <cfRule type="cellIs" priority="172" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="173" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="174" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C76">
     <cfRule type="cellIs" priority="175" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2547,29 +2602,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C77">
+    <cfRule type="cellIs" priority="178" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="179" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="180" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C78">
-    <cfRule type="cellIs" priority="178" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="179" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="180" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="181" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="182" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="183" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C79">
-    <cfRule type="cellIs" priority="181" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="182" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="183" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C80">
     <cfRule type="cellIs" priority="184" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2591,29 +2646,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C82">
+    <cfRule type="cellIs" priority="190" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="191" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="192" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C83">
-    <cfRule type="cellIs" priority="190" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="191" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="192" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="193" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="194" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="195" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C84">
-    <cfRule type="cellIs" priority="193" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="194" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="195" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C85">
     <cfRule type="cellIs" priority="196" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2635,29 +2690,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C87">
+    <cfRule type="cellIs" priority="202" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="203" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="204" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C88">
-    <cfRule type="cellIs" priority="202" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="203" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="204" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="205" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="206" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="207" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C89">
-    <cfRule type="cellIs" priority="205" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="206" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="207" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C90">
     <cfRule type="cellIs" priority="208" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2679,29 +2734,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C92">
+    <cfRule type="cellIs" priority="214" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="215" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="216" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="cellIs" priority="214" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="215" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="216" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="217" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="218" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="219" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C94">
-    <cfRule type="cellIs" priority="217" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="218" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="219" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C95">
     <cfRule type="cellIs" priority="220" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2723,29 +2778,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C97">
+    <cfRule type="cellIs" priority="226" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="227" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="228" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C98">
-    <cfRule type="cellIs" priority="226" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="227" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="228" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="229" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="230" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="231" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C99">
-    <cfRule type="cellIs" priority="229" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="230" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="231" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C100">
     <cfRule type="cellIs" priority="232" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2756,73 +2811,73 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C101">
+    <cfRule type="cellIs" priority="235" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="236" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="237" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="cellIs" priority="235" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="236" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="237" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="238" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="239" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="240" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103">
-    <cfRule type="cellIs" priority="238" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="239" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="240" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="241" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="242" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="243" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C104">
-    <cfRule type="cellIs" priority="241" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="242" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="243" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="244" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="245" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="246" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C106">
-    <cfRule type="cellIs" priority="244" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="245" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="246" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="247" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="248" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="249" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C107">
-    <cfRule type="cellIs" priority="247" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="248" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="249" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="250" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="251" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="252" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C108">
-    <cfRule type="cellIs" priority="250" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="251" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="252" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C110">
     <cfRule type="cellIs" priority="253" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2833,30 +2888,85 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C109">
+    <cfRule type="cellIs" priority="256" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="257" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="258" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C111">
-    <cfRule type="cellIs" priority="256" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="257" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="258" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="259" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="260" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="261" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C112">
-    <cfRule type="cellIs" priority="259" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="260" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="261" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="262" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="263" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="264" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C113">
+    <cfRule type="cellIs" priority="265" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="266" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="267" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C115">
+    <cfRule type="cellIs" priority="268" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="269" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="270" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C116">
+    <cfRule type="cellIs" priority="271" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="272" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="273" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C117">
+    <cfRule type="cellIs" priority="274" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="275" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="276" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C3 C4 C5 C6 C8 C9 C10 C11 C13 C14 C15 C16 C18 C19 C20 C21 C23 C24 C25 C26 C28 C29 C30 C31 C33 C34 C35 C36 C38 C39 C40 C41 C43 C44 C45 C46 C48 C49 C50 C51 C53 C54 C55 C56 C58 C59 C60 C62 C63 C64 C66 C67 C68 C70 C71 C72 C74 C75 C76 C78 C79 C80 C81 C83 C84 C85 C86 C88 C89 C90 C91 C93 C94 C95 C96 C98 C99 C100 C102 C103 C104 C106 C107 C108 C110 C111 C112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="R = not yet, A = getting there, G = confident" type="list">
+    <dataValidation sqref="C3 C4 C5 C6 C8 C9 C10 C11 C13 C14 C15 C16 C18 C19 C20 C21 C23 C24 C25 C26 C28 C29 C30 C31 C33 C34 C35 C36 C38 C39 C40 C41 C43 C44 C45 C46 C48 C49 C50 C51 C53 C54 C55 C56 C58 C59 C60 C61 C63 C64 C65 C66 C68 C69 C70 C71 C73 C74 C75 C77 C78 C79 C81 C82 C83 C84 C86 C87 C88 C89 C91 C92 C93 C94 C96 C97 C98 C99 C101 C102 C103 C104 C106 C107 C108 C109 C111 C112 C113 C115 C116 C117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="R = not yet, A = getting there, G = confident" type="list">
       <formula1>"R,A,G"</formula1>
     </dataValidation>
   </dataValidations>

--- a/0 Planning/Personal Learning Checklist.xlsx
+++ b/0 Planning/Personal Learning Checklist.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1382,7 +1382,7 @@
       <c r="A73" s="4" t="inlineStr"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Identify and describe the four key Acts: the Data Protection Act 1998/2018 (with GDPR), the Computer Misuse Act 1990, the Copyright, Designs &amp; Patents Act 1988 and the Regulation of Investigatory Powers Act 2000.</t>
+          <t>I can state what each of the four Acts covers: DPA 2018, CMA 1990, CDPA 1988 and RIPA 2000.</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       <c r="A74" s="4" t="inlineStr"/>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Select the correct law (and Computer Misuse Act offence) that applies to a given computing scenario, naming the responsible party.</t>
+          <t>I can name the DPA principles and data subject rights, and distinguish controller, processor and subject.</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr"/>
@@ -1404,7 +1404,7 @@
       <c r="A75" s="4" t="inlineStr"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Explain why more than one law can apply to a single scenario, distinguishing between the wrongdoing of each party involved.</t>
+          <t>I can classify a scenario against the three CMA offences and its later amendments.</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr"/>
@@ -1412,36 +1412,36 @@
       <c r="E75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr"/>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>I can apply the 'which Act, which section, why' method to unseen scenarios, including where two laws apply.</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr"/>
+      <c r="D76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>1.5.2</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Moral and Ethical Issues</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr"/>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Describe the key moral, ethical, cultural and social issues raised by computing, identifying both a benefit and a drawback for each.</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="4" t="inlineStr"/>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Identify the stakeholders affected by a computing decision and explain how the same fact can benefit one group while harming another.</t>
+          <t>I can describe the benefits and harms of each named issue area, from workforce automation to character sets.</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       <c r="A79" s="4" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Structure a balanced levels-of-response 'discuss' answer that weighs both sides and reaches a justified conclusion.</t>
+          <t>I can identify the stakeholders in a computing decision and explain how one fact helps one group while harming another.</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr"/>
@@ -1460,25 +1460,21 @@
       <c r="E79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Abstractly</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr"/>
+      <c r="A80" s="4" t="inlineStr"/>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>I can plan a levels-of-response 'discuss' answer: stakeholders, developed points both ways, weighed conclusion.</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>I can explain the nature and need for abstraction: removing detail irrelevant to the problem</t>
+          <t>I can link ethical issues to the legislation from 1.5.1 where relevant, such as monitoring to RIPA and profiling to the DPA.</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr"/>
@@ -1486,21 +1482,25 @@
       <c r="E81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr"/>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>I can distinguish representational abstraction from generalisation, with a valid example of each</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr"/>
-      <c r="D82" s="4" t="inlineStr"/>
-      <c r="E82" s="4" t="inlineStr"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Abstractly</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr"/>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>I can compare an abstraction with reality and justify which details are kept or discarded for a purpose</t>
+          <t>I can explain the nature and need for abstraction: removing detail irrelevant to the problem</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       <c r="A84" s="4" t="inlineStr"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>I can devise an abstract model for a given real-world scenario</t>
+          <t>I can distinguish representational abstraction from generalisation, with a valid example of each</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr"/>
@@ -1519,25 +1519,21 @@
       <c r="E84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>2.1.2</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Ahead</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
+      <c r="A85" s="4" t="inlineStr"/>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>I can compare an abstraction with reality and justify which details are kept or discarded for a purpose</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr"/>
+      <c r="D85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr"/>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>I can identify the inputs and outputs of a routine, distinguishing them from internal processes.</t>
+          <t>I can devise an abstract model for a given real-world scenario</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr"/>
@@ -1545,21 +1541,25 @@
       <c r="E86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr"/>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>I can state preconditions for a routine and explain the consequences of not meeting them.</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr"/>
-      <c r="D87" s="4" t="inlineStr"/>
-      <c r="E87" s="4" t="inlineStr"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2.1.2</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Ahead</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>I can explain caching and prefetching, pairing each benefit with its trade-off.</t>
+          <t>I can identify the inputs and outputs of a routine, distinguishing them from internal processes.</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr"/>
@@ -1570,7 +1570,7 @@
       <c r="A89" s="4" t="inlineStr"/>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>I can justify the use of reusable program components in a given scenario.</t>
+          <t>I can state preconditions for a routine and explain the consequences of not meeting them.</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr"/>
@@ -1578,25 +1578,21 @@
       <c r="E89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>2.1.3</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Procedurally</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="A90" s="4" t="inlineStr"/>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>I can explain caching and prefetching, pairing each benefit with its trade-off.</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Identify the components of a problem and decompose it into smaller sub-problems.</t>
+          <t>I can justify the use of reusable program components in a given scenario.</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr"/>
@@ -1604,21 +1600,25 @@
       <c r="E91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr"/>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Identify the components of a solution as named sub-procedures, each doing one clear job.</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2.1.3</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Procedurally</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Determine and justify the order of steps needed to solve a problem using data dependencies.</t>
+          <t>Identify the components of a problem and decompose it into smaller sub-problems.</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr"/>
@@ -1629,7 +1629,7 @@
       <c r="A94" s="4" t="inlineStr"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Explain the benefits of a modular, procedural solution for building, testing and maintenance.</t>
+          <t>Identify the components of a solution as named sub-procedures, each doing one clear job.</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr"/>
@@ -1637,25 +1637,21 @@
       <c r="E94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>2.1.4</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Logically</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr"/>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="inlineStr"/>
+      <c r="A95" s="4" t="inlineStr"/>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Determine and justify the order of steps needed to solve a problem using data dependencies.</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr"/>
+      <c r="D95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr"/>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Identify the points in a problem or program where a decision has to be taken.</t>
+          <t>Explain the benefits of a modular, procedural solution for building, testing and maintenance.</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr"/>
@@ -1663,21 +1659,25 @@
       <c r="E96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr"/>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Determine the exact Boolean conditions, using comparison and logical operators, that affect each decision's outcome.</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="inlineStr"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2.1.4</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Logically</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr"/>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Explain how decisions determine the flow of control through selection and iteration, stating both branches.</t>
+          <t>Identify the points in a problem or program where a decision has to be taken.</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr"/>
@@ -1688,7 +1688,7 @@
       <c r="A99" s="4" t="inlineStr"/>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Verify the logical flow of a routine using a trace table and correct common logic errors.</t>
+          <t>Determine the exact Boolean conditions, using comparison and logical operators, that affect each decision's outcome.</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr"/>
@@ -1696,25 +1696,21 @@
       <c r="E99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>2.1.5</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Thinking Concurrently</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr"/>
-      <c r="D100" s="2" t="inlineStr"/>
-      <c r="E100" s="2" t="inlineStr"/>
+      <c r="A100" s="4" t="inlineStr"/>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Explain how decisions determine the flow of control through selection and iteration, stating both branches.</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr"/>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>I can explain what it means for parts of a problem to be carried out concurrently.</t>
+          <t>Verify the logical flow of a routine using a trace table and correct common logic errors.</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr"/>
@@ -1722,21 +1718,25 @@
       <c r="E101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr"/>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>I can identify which tasks in a scenario can run at the same time by checking for data dependencies.</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr"/>
-      <c r="D102" s="4" t="inlineStr"/>
-      <c r="E102" s="4" t="inlineStr"/>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2.1.5</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Thinking Concurrently</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>I can weigh the benefits of concurrency (speed, responsiveness, hardware use) against its trade-offs (shared data, coordination, testing).</t>
+          <t>I can explain what it means for parts of a problem to be carried out concurrently.</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       <c r="A104" s="4" t="inlineStr"/>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>I can distinguish true parallel processing on multiple cores from concurrency by time-slicing on one core.</t>
+          <t>I can identify which tasks in a scenario can run at the same time by checking for data dependencies.</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr"/>
@@ -1755,25 +1755,21 @@
       <c r="E104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>2.2.1</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Programming Techniques</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr"/>
-      <c r="E105" s="2" t="inlineStr"/>
+      <c r="A105" s="4" t="inlineStr"/>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>I can weigh the benefits of concurrency (speed, responsiveness, hardware use) against its trade-offs (shared data, coordination, testing).</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr"/>
+      <c r="D105" s="4" t="inlineStr"/>
+      <c r="E105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr"/>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>I can use sequence, branching and both count- and condition-controlled iteration in OCR Exam Reference Language.</t>
+          <t>I can distinguish true parallel processing on multiple cores from concurrency by time-slicing on one core.</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr"/>
@@ -1781,21 +1777,25 @@
       <c r="E106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr"/>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>I can trace a recursive subroutine using stack frames, identify its base case, and compare recursion with iteration.</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr"/>
-      <c r="D107" s="4" t="inlineStr"/>
-      <c r="E107" s="4" t="inlineStr"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2.2.1</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Programming Techniques</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr"/>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr"/>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>I can explain scope, distinguish functions from procedures, and predict the effect of passing parameters by value and by reference.</t>
+          <t>I can use sequence, branching and both count- and condition-controlled iteration in OCR Exam Reference Language.</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr"/>
@@ -1806,7 +1806,7 @@
       <c r="A109" s="4" t="inlineStr"/>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>I can describe IDE features that help build and debug code, and apply OOP techniques: encapsulation, inheritance and polymorphism.</t>
+          <t>I can trace a recursive subroutine using stack frames, identify its base case, and compare recursion with iteration.</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr"/>
@@ -1814,25 +1814,21 @@
       <c r="E109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>2.2.2</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Computational Methods</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="A110" s="4" t="inlineStr"/>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>I can explain scope, distinguish functions from procedures, and predict the effect of passing parameters by value and by reference.</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr"/>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>State the features that make a problem solvable computationally and recognise non-computable and intractable problems</t>
+          <t>I can describe IDE features that help build and debug code, and apply OOP techniques: encapsulation, inheritance and polymorphism.</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr"/>
@@ -1840,21 +1836,25 @@
       <c r="E111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr"/>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>Describe problem recognition, decomposition, divide and conquer, and abstraction (representational and by generalisation)</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr"/>
-      <c r="D112" s="4" t="inlineStr"/>
-      <c r="E112" s="4" t="inlineStr"/>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2.2.2</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Computational Methods</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr"/>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr"/>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Apply named computational methods (backtracking, data mining, heuristics, performance modelling, pipelining, visualisation) to suitable problems, justifying why each fits</t>
+          <t>I can state the features that make a problem solvable computationally, and recognise non-computable and intractable problems.</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr"/>
@@ -1862,25 +1862,21 @@
       <c r="E113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>2.3.1</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Algorithms</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr"/>
-      <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="2" t="inlineStr"/>
+      <c r="A114" s="4" t="inlineStr"/>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>I can distinguish decomposition from divide and conquer, and representational abstraction from abstraction by generalisation.</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr"/>
+      <c r="D114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr"/>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Use Big O notation to express and justify the time and space complexity of an algorithm, simplifying expressions to the dominant term.</t>
+          <t>I can trace a backtracking solution to a maze or constraint problem, showing each dead end and retreat.</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr"/>
@@ -1891,7 +1887,7 @@
       <c r="A116" s="4" t="inlineStr"/>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Compare standard searching and sorting algorithms by how they work and their best, average and worst-case complexities.</t>
+          <t>I can match backtracking, data mining, heuristics, performance modelling, pipelining and visualisation to suitable problems and justify why each fits.</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr"/>
@@ -1899,57 +1895,105 @@
       <c r="E116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr"/>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Describe and trace algorithms on data structures, including tree traversals and the shortest-path algorithms Dijkstra and A*.</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr"/>
-      <c r="D117" s="4" t="inlineStr"/>
-      <c r="E117" s="4" t="inlineStr"/>
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2.3.1</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Algorithms (part 1 — analysis, Big O and searching)</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr"/>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr"/>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>I can analyse an algorithm and justify its suitability for a given task.</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr"/>
+      <c r="D118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="B119" s="6" t="inlineStr">
+      <c r="A119" s="4" t="inlineStr"/>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>I can express the time and space complexity of an algorithm in Big O notation, simplifying to the dominant term.</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr"/>
+      <c r="D119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr"/>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>I can distinguish best, average and worst case and state each for linear and binary search.</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr"/>
+      <c r="D120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr"/>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>I can write and trace linear and binary search in OCR Exam Reference Language and justify O(n) versus O(log n).</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr"/>
+      <c r="D121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>🔴 Not yet (R):</t>
         </is>
       </c>
-      <c r="C119">
-        <f>COUNTIF(C2:C117,"R")</f>
+      <c r="C123">
+        <f>COUNTIF(C2:C121,"R")</f>
         <v/>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" s="6" t="inlineStr">
+    <row r="124">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>🟠 Getting there (A):</t>
         </is>
       </c>
-      <c r="C120">
-        <f>COUNTIF(C2:C117,"A")</f>
+      <c r="C124">
+        <f>COUNTIF(C2:C121,"A")</f>
         <v/>
       </c>
     </row>
-    <row r="121">
-      <c r="B121" s="6" t="inlineStr">
+    <row r="125">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>🟢 Confident (G):</t>
         </is>
       </c>
-      <c r="C121">
-        <f>COUNTIF(C2:C117,"G")</f>
+      <c r="C125">
+        <f>COUNTIF(C2:C121,"G")</f>
         <v/>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" s="7" t="inlineStr">
+    <row r="126">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>Total objectives:</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>92</v>
+      <c r="C126" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2602,7 +2646,7 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
+  <conditionalFormatting sqref="C76">
     <cfRule type="cellIs" priority="178" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2635,18 +2679,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C80">
+    <cfRule type="cellIs" priority="187" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="188" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="189" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C81">
-    <cfRule type="cellIs" priority="187" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="188" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="189" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C82">
     <cfRule type="cellIs" priority="190" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2679,18 +2723,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C85">
+    <cfRule type="cellIs" priority="199" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="200" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="201" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C86">
-    <cfRule type="cellIs" priority="199" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="200" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="201" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C87">
     <cfRule type="cellIs" priority="202" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2723,18 +2767,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C90">
+    <cfRule type="cellIs" priority="211" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="212" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="213" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C91">
-    <cfRule type="cellIs" priority="211" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="212" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="213" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C92">
     <cfRule type="cellIs" priority="214" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2767,18 +2811,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C95">
+    <cfRule type="cellIs" priority="223" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="224" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="225" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C96">
-    <cfRule type="cellIs" priority="223" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="224" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="225" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C97">
     <cfRule type="cellIs" priority="226" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2811,18 +2855,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C100">
+    <cfRule type="cellIs" priority="235" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="236" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="237" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C101">
-    <cfRule type="cellIs" priority="235" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="236" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="237" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C102">
     <cfRule type="cellIs" priority="238" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2855,18 +2899,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C105">
+    <cfRule type="cellIs" priority="247" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="248" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="249" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C106">
-    <cfRule type="cellIs" priority="247" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="248" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="249" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C107">
     <cfRule type="cellIs" priority="250" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2899,18 +2943,18 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C110">
+    <cfRule type="cellIs" priority="259" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="260" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="261" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C111">
-    <cfRule type="cellIs" priority="259" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="260" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="261" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C112">
     <cfRule type="cellIs" priority="262" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2932,29 +2976,29 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C114">
+    <cfRule type="cellIs" priority="268" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="269" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="270" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C115">
-    <cfRule type="cellIs" priority="268" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="269" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="270" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="271" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="272" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="273" operator="equal" dxfId="2">
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C116">
-    <cfRule type="cellIs" priority="271" operator="equal" dxfId="0">
-      <formula>"R"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="272" operator="equal" dxfId="1">
-      <formula>"A"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="273" operator="equal" dxfId="2">
-      <formula>"G"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C117">
     <cfRule type="cellIs" priority="274" operator="equal" dxfId="0">
       <formula>"R"</formula>
     </cfRule>
@@ -2965,8 +3009,52 @@
       <formula>"G"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C118">
+    <cfRule type="cellIs" priority="277" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="278" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="279" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C119">
+    <cfRule type="cellIs" priority="280" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="281" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="282" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C120">
+    <cfRule type="cellIs" priority="283" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="284" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="285" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C121">
+    <cfRule type="cellIs" priority="286" operator="equal" dxfId="0">
+      <formula>"R"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="287" operator="equal" dxfId="1">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="288" operator="equal" dxfId="2">
+      <formula>"G"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C3 C4 C5 C6 C8 C9 C10 C11 C13 C14 C15 C16 C18 C19 C20 C21 C23 C24 C25 C26 C28 C29 C30 C31 C33 C34 C35 C36 C38 C39 C40 C41 C43 C44 C45 C46 C48 C49 C50 C51 C53 C54 C55 C56 C58 C59 C60 C61 C63 C64 C65 C66 C68 C69 C70 C71 C73 C74 C75 C77 C78 C79 C81 C82 C83 C84 C86 C87 C88 C89 C91 C92 C93 C94 C96 C97 C98 C99 C101 C102 C103 C104 C106 C107 C108 C109 C111 C112 C113 C115 C116 C117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="R = not yet, A = getting there, G = confident" type="list">
+    <dataValidation sqref="C3 C4 C5 C6 C8 C9 C10 C11 C13 C14 C15 C16 C18 C19 C20 C21 C23 C24 C25 C26 C28 C29 C30 C31 C33 C34 C35 C36 C38 C39 C40 C41 C43 C44 C45 C46 C48 C49 C50 C51 C53 C54 C55 C56 C58 C59 C60 C61 C63 C64 C65 C66 C68 C69 C70 C71 C73 C74 C75 C76 C78 C79 C80 C81 C83 C84 C85 C86 C88 C89 C90 C91 C93 C94 C95 C96 C98 C99 C100 C101 C103 C104 C105 C106 C108 C109 C110 C111 C113 C114 C115 C116 C118 C119 C120 C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="R = not yet, A = getting there, G = confident" type="list">
       <formula1>"R,A,G"</formula1>
     </dataValidation>
   </dataValidations>
